--- a/COST_REFERENCE_1410.xlsx
+++ b/COST_REFERENCE_1410.xlsx
@@ -102,30 +102,44 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,7 +504,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -511,1033 +525,1060 @@
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Одежда: средняя себестоимость с доставкой по открытым ценам российских фабрик и оптовиков (14.10.2026)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Средняя = среднее по серединам диапазонов всех сайтов. Опт = среднее только по фабричным/оптовым ценам (если есть). Доставка ТК: центр 15, регионы 35, Север 120 ₽/кг × вес [оценка].</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="66" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Сайтов</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Мин., ₽</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Макс., ₽</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Средняя по рынку, ₽</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Средняя опт/фабрика, ₽</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Себестоимость для расчёта, ₽</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Вес, кг</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>С доставкой: Центр (Москва/МО, ЦФО), ₽</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>С доставкой: Регионы (Урал, Юг, Сибирь), ₽</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>С доставкой: Крайний Север / Якутия / ДВ, ₽</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Ваша себестоимость, ₽</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Медиана НМЦК 44-ФЗ, ₽</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Наценка к медиане НМЦК (центр)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Костюм летний рабочий</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="6" t="n">
         <v>938</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="6" t="n">
         <v>4984</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="6" t="n">
         <v>2731.2</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="6" t="n">
         <v>1685.75</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="6" t="n">
         <v>3500</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="6" t="n">
         <v>3518</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="6" t="n">
         <v>3542</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="6" t="n">
         <v>3644</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="6" t="n">
         <v>3500</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="6" t="n">
         <v>4122</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="7" t="n">
         <v>0.1716884593519046</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Костюм летний спасателя/МЧС</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="6" t="n">
         <v>2490</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="6" t="n">
         <v>6675</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="6" t="n">
         <v>4275</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="6" t="n">
         <v>2490</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="6" t="n">
         <v>3500</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="6" t="n">
         <v>3519.5</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="6" t="n">
         <v>3545.5</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="6" t="n">
         <v>3656</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="6" t="n">
         <v>3500</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="6" t="n">
         <v>4122</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="7" t="n">
         <v>0.171189089359284</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="6" t="n">
         <v>2040</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="6" t="n">
         <v>9394</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="6" t="n">
         <v>5103.5</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="6" t="n">
         <v>3737.7</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="6" t="n">
         <v>5039</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="6" t="n">
         <v>5091</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="6" t="n">
         <v>5312</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="6" t="n">
         <v>7768</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="8" t="n">
         <v>0.541575709466164</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Костюм зимний северный (IV/особый пояс)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="6" t="n">
         <v>4600</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="6" t="n">
         <v>23998</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="6" t="n">
         <v>10619.125</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="6" t="n">
         <v>6571.5</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="6" t="n">
         <v>6571.5</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="6" t="n">
         <v>6619.5</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="6" t="n">
         <v>6683.5</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="6" t="n">
         <v>6955.5</v>
       </c>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n">
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n">
         <v>7768</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="7" t="n">
         <v>0.1735025304025983</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Комбинезон летний</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="6" t="n">
         <v>3766</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="6" t="n">
         <v>4102</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="6" t="n">
         <v>3934</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="6" t="n">
         <v>3934</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="6" t="n">
         <v>3540.6</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="6" t="n">
         <v>3557.1</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="6" t="n">
         <v>3579.1</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="6" t="n">
         <v>3672.6</v>
       </c>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Комбинезон зимний</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="6" t="n">
         <v>10199</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="6" t="n">
         <v>10577</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="6" t="n">
         <v>10388</v>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n">
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n">
         <v>9349.200000000001</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="6" t="n">
         <v>9385.200000000001</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="6" t="n">
         <v>9433.200000000001</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="6" t="n">
         <v>9637.200000000001</v>
       </c>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Куртка утепленная</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="6" t="n">
         <v>1125</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="6" t="n">
         <v>4995</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="6" t="n">
         <v>3004.4</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="6" t="n">
         <v>2147.333333333333</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="6" t="n">
         <v>2147.333333333333</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="6" t="n">
         <v>2171.333333333333</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="6" t="n">
         <v>2203.333333333333</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="6" t="n">
         <v>2339.333333333333</v>
       </c>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n">
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n">
         <v>4500</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="N10" s="8" t="n">
         <v>1.072459318391157</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Полукомбинезон / брюки зимние</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="6" t="n">
         <v>720</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="6" t="n">
         <v>3750</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="6" t="n">
         <v>1992.375</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="6" t="n">
         <v>850.25</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>850.25</v>
-      </c>
-      <c r="H11" s="3" t="n">
+      <c r="G11" s="6" t="n">
+        <v>1793.1375</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="n">
-        <v>865.25</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>885.25</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>970.25</v>
-      </c>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n">
+      <c r="I11" s="6" t="n">
+        <v>1808.1375</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1828.1375</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>1913.1375</v>
+      </c>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n">
         <v>4005</v>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>3.628720023114707</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="N11" s="8" t="n">
+        <v>1.214986415579567</v>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Футболка</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="6" t="n">
         <v>211</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="6" t="n">
         <v>488</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="6" t="n">
         <v>422.625</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="6" t="n">
         <v>240.5</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="6" t="n">
         <v>240.5</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="6" t="n">
         <v>243.5</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="6" t="n">
         <v>247.5</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" s="6" t="n">
         <v>264.5</v>
       </c>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n">
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n">
         <v>562</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="8" t="n">
         <v>1.308008213552361</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Халат рабочий</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="6" t="n">
         <v>1466</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="6" t="n">
         <v>831.6666666666666</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="6" t="n">
         <v>618.25</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="6" t="n">
         <v>618.25</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="6" t="n">
         <v>625.75</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="6" t="n">
         <v>635.75</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K13" s="6" t="n">
         <v>678.25</v>
       </c>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n">
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n">
         <v>1288</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="8" t="n">
         <v>1.058330003995206</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Жилет утепленный</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="6" t="n">
         <v>1190</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="6" t="n">
         <v>2788</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="6" t="n">
         <v>1978.333333333333</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="6" t="n">
         <v>1281</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="6" t="n">
         <v>1281</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="6" t="n">
         <v>1291.5</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="6" t="n">
         <v>1305.5</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K14" s="6" t="n">
         <v>1365</v>
       </c>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Жилет сигнальный</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="6" t="n">
         <v>260</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="6" t="n">
         <v>753</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="6" t="n">
         <v>427.75</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="6" t="n">
         <v>290</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="6" t="n">
         <v>290</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="6" t="n">
         <v>292.25</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="6" t="n">
         <v>295.25</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K15" s="6" t="n">
         <v>308</v>
       </c>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n">
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n">
         <v>664</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="8" t="n">
         <v>1.272027373823781</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Ботинки кожаные с МП (летние)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="6" t="n">
         <v>3018</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="6" t="n">
         <v>3416</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="6" t="n">
         <v>3300.25</v>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n">
         <v>2970.225</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="6" t="n">
         <v>2994.225</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="6" t="n">
         <v>3026.225</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K16" s="6" t="n">
         <v>3162.225</v>
       </c>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n">
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n">
         <v>3308</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="N16" s="7" t="n">
         <v>0.1047933939500205</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Ботинки утепленные</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="6" t="n">
         <v>2174</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="6" t="n">
         <v>5511</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="6" t="n">
         <v>4220.833333333333</v>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n">
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n">
         <v>3798.75</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="6" t="n">
         <v>3827.25</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="6" t="n">
         <v>3865.25</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="K17" s="6" t="n">
         <v>4026.75</v>
       </c>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n">
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n">
         <v>4485</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="N17" s="7" t="n">
         <v>0.1718596903782088</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Сапоги ПВХ</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="6" t="n">
         <v>620</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="6" t="n">
         <v>1184</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="6" t="n">
         <v>1012</v>
       </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n">
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n">
         <v>910.8000000000001</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="6" t="n">
         <v>931.8000000000001</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="6" t="n">
         <v>959.8000000000001</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="K18" s="6" t="n">
         <v>1078.8</v>
       </c>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n">
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n">
         <v>1415</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="8" t="n">
         <v>0.5185662159261644</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Костюм сварщика</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="6" t="n">
         <v>3801</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="6" t="n">
         <v>7020</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="6" t="n">
         <v>6311.5</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="6" t="n">
         <v>6993</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="6" t="n">
         <v>5680.35</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="6" t="n">
         <v>5725.35</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="6" t="n">
         <v>5785.35</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="K19" s="6" t="n">
         <v>6040.35</v>
       </c>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n">
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n">
         <v>10625</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="8" t="n">
         <v>0.8557817426008889</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Костюм от электродуги</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="6" t="n">
         <v>17008</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="6" t="n">
         <v>33155</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="6" t="n">
         <v>24638.25</v>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n">
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n">
         <v>22174.425</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="6" t="n">
         <v>22204.425</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="6" t="n">
         <v>22244.425</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="K20" s="6" t="n">
         <v>22414.425</v>
       </c>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n">
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n">
         <v>14215</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="10" t="n">
         <v>-0.3598122896674875</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Костюм от нефтепродуктов</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="6" t="n">
         <v>6731</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="6" t="n">
         <v>24199</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="6" t="n">
         <v>13850.5</v>
       </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n">
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n">
         <v>12465.45</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="6" t="n">
         <v>12495.45</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="6" t="n">
         <v>12535.45</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="K21" s="6" t="n">
         <v>12705.45</v>
       </c>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Термобельё (комплект)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="6" t="n">
         <v>1428</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="6" t="n">
         <v>2892</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="6" t="n">
         <v>2160</v>
       </c>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n">
         <v>1944</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="6" t="n">
         <v>1950</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="6" t="n">
         <v>1958</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="K22" s="6" t="n">
         <v>1992</v>
       </c>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n">
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n">
         <v>1632</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="10" t="n">
         <v>-0.1630769230769231</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Перчатки х/б с ПВХ (пара)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="6" t="n">
         <v>40.5</v>
       </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n">
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n">
         <v>36.45</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="5" t="n">
         <v>0.08</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="6" t="n">
         <v>37.65000000000001</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="6" t="n">
         <v>39.25</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="K23" s="6" t="n">
         <v>46.05</v>
       </c>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n">
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="8" t="n">
         <v>2.426294820717131</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Рукавицы (пара)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="6" t="n">
         <v>149</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="6" t="n">
         <v>129.25</v>
       </c>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n">
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n">
         <v>116.325</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="6" t="n">
         <v>118.575</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="6" t="n">
         <v>121.575</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="K24" s="6" t="n">
         <v>134.325</v>
       </c>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n">
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n">
         <v>328</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="8" t="n">
         <v>1.76618174151381</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Каска</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="6" t="n">
         <v>303</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="6" t="n">
         <v>488</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="6" t="n">
         <v>395.5</v>
       </c>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n">
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n">
         <v>355.95</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="I25" s="6" t="n">
         <v>361.95</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="6" t="n">
         <v>369.95</v>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="K25" s="6" t="n">
         <v>403.95</v>
       </c>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n">
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n">
         <v>964</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="8" t="n">
         <v>1.663351291614864</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:N25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1545,7 +1586,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1559,2183 +1600,2183 @@
     <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Производитель / город</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Цена от, ₽</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Цена до, ₽</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Тип цены</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Костюм летний рабочий</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Иваново, фабрика</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="12" t="n">
         <v>938</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="12" t="n">
         <v>1715</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/kostumy/</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Костюм летний рабочий</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>ivsoteks.ru</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Иваново</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>1600</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="12" t="n">
         <v>2490</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>https://ivsoteks.ru/specodejda</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Костюм летний рабочий</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>2321</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>3065</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Костюм летний рабочий</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Тракт</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>3086</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>3746</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/11954/</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Костюм летний рабочий</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>3367</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>4984</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/letnyaya/</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Костюм летний спасателя/МЧС</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>productcenter.ru</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>«Аврора», Барнаул</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>2490</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>2490</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>https://productcenter.ru/products/45461/kostiumy-dlia-sotrudnikov-mchs</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Костюм летний спасателя/МЧС</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>voen36.ru</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Воен36, Воронеж (собств. пр-во)</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>3100</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>5995</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>розница</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>https://voen36.ru/catalog/forma_mchs/</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Костюм летний спасателя/МЧС</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>barrakuda.biz</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Барракуда, Москва</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>4900</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>6675</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>розница</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>https://barrakuda.biz/formennaya-odezhda/kostyumy-mchs</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>fabrikant-textile.ru</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Фабрикант, Иваново</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>2040</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>2460</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>spec-standart.ru</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Стандарт Спецодежда, Иваново</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>2570</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>4968</v>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>specteks37.ru</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>СпецТекс 37, Иваново</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>2650</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>4600</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>ivsoteks.ru</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Ивсотекс, Иваново</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>2900</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>5830</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>https://ivsoteks.ru/specodejda</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Иваново, фабрика</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>3549</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>5810</v>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/kostyumy-1/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Тракт</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>3588</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>7793</v>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12066/</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>6084</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>9394</v>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/odezhda_zimnyaya/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний рабочий (I–III пояс)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>8262</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>9158</v>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний северный (IV/особый пояс)</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>specteks37.ru</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>СпецТекс 37 №265 (IV пояс)</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <v>4600</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <v>4600</v>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний северный (IV/особый пояс)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>spec-standart.ru</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>«Север» (тройка), Иваново</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>8543</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>8543</v>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний северный (IV/особый пояс)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Тракт «Беринг» / «Северный шельф»</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>9659</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>23998</v>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/13086/</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Костюм зимний северный (IV/особый пояс)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение «Надым» / «Ураган»</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <v>9760</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>15250</v>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/odezhda_zimnyaya/</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Комбинезон летний</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Иваново, фабрика</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <v>3766</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>4102</v>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/kombinezony/</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Комбинезон зимний</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение «Пилот»</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>10199</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="12" t="n">
         <v>10577</v>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/odezhda_zimnyaya/</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Куртка утепленная</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>fabrikant-textile.ru</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Фабрикант, Иваново</t>
         </is>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="12" t="n">
         <v>1125</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>1695</v>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Куртка утепленная</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>specteks37.ru</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>СпецТекс 37</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="12" t="n">
         <v>1200</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="12" t="n">
         <v>2620</v>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>https://www.specteks37.ru/katalog/zimnyaya-spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Куртка утепленная</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Иваново, фабрика</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="12" t="n">
         <v>1764</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <v>4480</v>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Куртка утепленная</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="12" t="n">
         <v>2501</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>4669</v>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Куртка утепленная</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Тракт (медиана)</t>
         </is>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="12" t="n">
         <v>4995</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <v>4995</v>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Полукомбинезон / брюки зимние</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>fabrikant-textile.ru</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Фабрикант</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="12" t="n">
         <v>765</v>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Полукомбинезон / брюки зимние</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>spec-standart.ru</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Стандарт Спецодежда</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="12" t="n">
         <v>958</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="12" t="n">
         <v>958</v>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>https://spec-standart.ru/zimnyaya-specodezhda</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Полукомбинезон / брюки зимние</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Тракт (медиана)</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="12" t="n">
         <v>2799</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>2799</v>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Полукомбинезон / брюки зимние</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="12" t="n">
         <v>3190</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="12" t="n">
         <v>3750</v>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Футболка</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>productcenter.ru</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>фабрики Иваново</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="12" t="n">
         <v>211</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>https://productcenter.ru/products/r-ivanovskaia-obl-168/c-ivanovo-2550/catalog-muzhskiie-futbolki-1062</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Футболка</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <v>478</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="12" t="n">
         <v>478</v>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Футболка</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Тракт</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="12" t="n">
         <v>484</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <v>484</v>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12012/</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Футболка</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/trikotazh/</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Халат рабочий</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>fabrikant-textile.ru</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Фабрикант</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Халат рабочий</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>Иваново, фабрика</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="12" t="n">
         <v>609</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="12" t="n">
         <v>1064</v>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/letnyaya-spetsodezhda/khalati/</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Халат рабочий</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="12" t="n">
         <v>1051</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="12" t="n">
         <v>1466</v>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Жилет утепленный</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>Иваново, фабрика</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="12" t="n">
         <v>1190</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="12" t="n">
         <v>1372</v>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Жилет утепленный</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Тракт</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="12" t="n">
         <v>1866</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="12" t="n">
         <v>1866</v>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12021/</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Жилет утепленный</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение «Сатурн»</t>
         </is>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="12" t="n">
         <v>2788</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="12" t="n">
         <v>2788</v>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/odezhda_dlya_okhrannykh_struktur/</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Жилет сигнальный</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>fabrikant-textile.ru</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Фабрикант</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="12" t="n">
         <v>260</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>https://fabrikant-textile.ru/catalog/spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Жилет сигнальный</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>Тракт</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="12" t="n">
         <v>316</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="12" t="n">
         <v>316</v>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/138206/</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Жилет сигнальный</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="12" t="n">
         <v>677</v>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Жилет сигнальный</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="12" t="n">
         <v>753</v>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Ботинки кожаные с МП (летние)</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>Техноавиа «Билд»</t>
         </is>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="12" t="n">
         <v>3018</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="12" t="n">
         <v>3351</v>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Ботинки кожаные с МП (летние)</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Тракт (медиана 42 моделей)</t>
         </is>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="12" t="n">
         <v>3416</v>
       </c>
-      <c r="E48" s="11" t="n">
+      <c r="E48" s="12" t="n">
         <v>3416</v>
       </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Ботинки утепленные</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>Тракт «Металлан»…«Тягач»</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="12" t="n">
         <v>2174</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="12" t="n">
         <v>4579</v>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12102/</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Ботинки утепленные</t>
         </is>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Техноавиа «Билд» утепл.</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="12" t="n">
         <v>3775</v>
       </c>
-      <c r="E50" s="11" t="n">
+      <c r="E50" s="12" t="n">
         <v>3775</v>
       </c>
-      <c r="F50" s="10" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Ботинки утепленные</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Тракт «Алтай» натур. мех</t>
         </is>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="12" t="n">
         <v>5511</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="12" t="n">
         <v>5511</v>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12598/</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Сапоги ПВХ</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="E52" s="11" t="n">
+      <c r="E52" s="12" t="n">
         <v>1184</v>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Сапоги ПВХ</t>
         </is>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение «Ямал» (утепл.)</t>
         </is>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="12" t="n">
         <v>1122</v>
       </c>
-      <c r="E53" s="11" t="n">
+      <c r="E53" s="12" t="n">
         <v>1122</v>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Костюм сварщика</t>
         </is>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Техноавиа КС01/КС21</t>
         </is>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D54" s="12" t="n">
         <v>3801</v>
       </c>
-      <c r="E54" s="11" t="n">
+      <c r="E54" s="12" t="n">
         <v>7020</v>
       </c>
-      <c r="F54" s="10" t="inlineStr">
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Костюм сварщика</t>
         </is>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>Тракт (медиана)</t>
         </is>
       </c>
-      <c r="D55" s="11" t="n">
+      <c r="D55" s="12" t="n">
         <v>6531</v>
       </c>
-      <c r="E55" s="11" t="n">
+      <c r="E55" s="12" t="n">
         <v>6531</v>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Костюм сварщика</t>
         </is>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>ivuniforma.ru</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>Иваново, утепл. со спилком</t>
         </is>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D56" s="12" t="n">
         <v>6993</v>
       </c>
-      <c r="E56" s="11" t="n">
+      <c r="E56" s="12" t="n">
         <v>6993</v>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>опт</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>https://www.ivuniforma.ru/catalog/rabochaya-odezhda/zimnjaja/kostyumy-1/</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Костюм от электродуги</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>Тракт летний (медиана) / зимний</t>
         </is>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="12" t="n">
         <v>17008</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E57" s="12" t="n">
         <v>33155</v>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
+      <c r="G57" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/61043/</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Костюм от электродуги</t>
         </is>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>Техноавиа «Вольт»</t>
         </is>
       </c>
-      <c r="D58" s="11" t="n">
+      <c r="D58" s="12" t="n">
         <v>24195</v>
       </c>
-      <c r="E58" s="11" t="n">
+      <c r="E58" s="12" t="n">
         <v>24195</v>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>Костюм от нефтепродуктов</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>Тракт летний / «Пластойл» зимний</t>
         </is>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="12" t="n">
         <v>6731</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E59" s="12" t="n">
         <v>11253</v>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12720/</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Костюм от нефтепродуктов</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>spets.ru</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Спецобъединение «Мегастатойл»</t>
         </is>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="12" t="n">
         <v>13219</v>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E60" s="12" t="n">
         <v>24199</v>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>https://www.spets.ru/products/spetsodezhda/odezhda_spetsialnaya/</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>Термобельё (комплект)</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>Тракт</t>
         </is>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="12" t="n">
         <v>1428</v>
       </c>
-      <c r="E61" s="11" t="n">
+      <c r="E61" s="12" t="n">
         <v>2892</v>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/product/12922/</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Перчатки х/б с ПВХ (пара)</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Техноавиа «Гриф»…«Техно»</t>
         </is>
       </c>
-      <c r="D62" s="11" t="n">
+      <c r="D62" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="E62" s="11" t="n">
+      <c r="E62" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Рукавицы (пара)</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>Техноавиа</t>
         </is>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E63" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G63" s="12" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Рукавицы (пара)</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>Тракт (медиана)</t>
         </is>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D64" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Каска</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>technoavia.ru</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>Техноавиа СОМЗ-55</t>
         </is>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D65" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="E65" s="11" t="n">
+      <c r="E65" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G65" s="12" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>https://files.technoavia.ru/files/price/11/price_Technoavia_moscow_2025_06_27_08_46_34.pdf</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>Каска</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>trakt.ru</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Тракт (медиана)</t>
         </is>
       </c>
-      <c r="D66" s="11" t="n">
+      <c r="D66" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="E66" s="11" t="n">
+      <c r="E66" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>прайс</t>
         </is>
       </c>
-      <c r="G66" s="12" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>https://www.trakt.ru/</t>
         </is>
@@ -3811,6 +3852,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3818,7 +3860,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3834,303 +3876,303 @@
     <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Соль техническая: себестоимость с доставкой до заказчика, ₽/т</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n"/>
-      <c r="C1" s="10" t="n"/>
-      <c r="D1" s="10" t="n"/>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="10" t="n"/>
-      <c r="G1" s="10" t="n"/>
-      <c r="H1" s="10" t="n"/>
-      <c r="I1" s="10" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Средняя реальная = среднее вариантов 2 (завод вагоном) и 3 (склад авто). Ваша КЗ-цена 2 500 — требует подтверждения точки доставки.</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Лот / регион</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Тонн</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Цена в НМЦК, ₽/т</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>1. Казахстан (ваша)</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2. Ближайший завод вагоном</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>3. Ближайший склад авто</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>4. Дилер с доставкой</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Средняя реальная (2–3), ₽/т</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Источник (ближайший)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>ДГХ, Московская обл.</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>16810</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>4770</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>4970</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" s="12" t="n">
         <v>4870</v>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>Беларуськалий, Солигорск</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Новосибирск, «Дзержинка»</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>4310</v>
       </c>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n">
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="12" t="n">
         <v>4310</v>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>Павлодарсоль (КЗ, Таволжан) / Алтайская соледоб. (Бурсоль)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Волоколамск, МО</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>12260</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>4650</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>5330</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="12" t="n">
         <v>4990</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Беларуськалий, Солигорск</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Абинск, Краснодарский край</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>9120</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>5090</v>
       </c>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n">
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="12" t="n">
         <v>5090</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>Баскунчак (Руссоль), Астраханская обл.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Воронеж</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="2" t="n">
         <v>461</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>7150</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>4650</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>7670</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="12" t="n">
         <v>6160</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>Баскунчак (Руссоль), Астраханская обл.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Струнино, Владимирская обл.</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>8950</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>4910</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>5210</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="12" t="n">
         <v>5060</v>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>Беларуськалий, Солигорск</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Самара (нужен опыт 24,2 млн)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="2" t="n">
         <v>11000</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>3850</v>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n">
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="12" t="n">
         <v>3850</v>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Илецксоль (Руссоль), Соль-Илецк</t>
         </is>
@@ -4138,6 +4180,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4145,7 +4188,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4158,693 +4201,693 @@
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Производитель</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Продукт / фасовка</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Цена от, ₽/т</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Условия</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>esolk.ru (ЕСК)</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Павлодарсоль / Аралтуз (Казахстан), Уралкалий, Белкалий, Тыреть, АСК</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Галит тип B/C, помол 2–3, навалом</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="12" t="n">
         <v>1990</v>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>без НДС, без доставки, от вагона (~70 т), станция отгрузки</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>https://www.esolk.ru/produktsiya/kontsentrat-mineralnyy-galit/mkr-1-tonna/</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Ваша цена</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Казахстан</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>МКР, НДС вкл., с доставкой в РФ</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>данные клиента — проверить, куда именно доставка</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>nsmgr.ru (Люберцы)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Тип D, от 40 т, россыпь/биг-бэг</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>4350</v>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>самовывоз, НДС не указан</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Тип D, до 40 т, россыпь/биг-бэг</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>4550</v>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>тендер Алтайский край (saby.ru)</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>НМЦК 2 430 т = 13,37 млн</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <v>5500</v>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>начальная цена заказчика, ориентир</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>https://saby.ru/tenders/card/245190387</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Илецкая (Руссоль)</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Тип C, россыпь</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <v>5750</v>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>без указания</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Тип C, россыпь/биг-бэг</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <v>6300</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/big-begi</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>nsmgr.ru</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Уралкалий / Белкалий</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Тип A с антислеживателем, биг-бэг</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <v>6500</v>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>https://nsmgr.ru/reagenty/tekhnicheskaya-sol/tip-a/uralkaliy-big-beg-s-antislezhivatelem</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>sknerud.ru (Москва)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Астрахань</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <v>6500</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Аралтуз / Индертуз / Алтайсоль (КЗ)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>7000</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>perevalka24.ru</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Уралкалий «Галит» марка А</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>биг-бэг 1000 кг</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>7000</v>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>«от»</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>https://perevalka24.ru/product/peskosol/kontsentrat-mineralnyy-galit-marki-a-big-beg-1000kg-1-tonna/</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>perevalka-tsk.ru (Москва)</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Аралтуз (КЗ)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>навалом</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="12" t="n">
         <v>7300</v>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>самовывоз; доставка 8–11 тыс. за машину 20–25 м³ до 60 км</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>https://perevalka-tsk.ru/product/pg-materialy/tekhnicheskaya-sol/tekhnicheskaya-sol-araltuz/</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Беларуськалий / Баскунчак</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="12" t="n">
         <v>7500</v>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>vektor-e.ru (Москва)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Аралтуз (КЗ)</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>МКР / россыпь, от 2 т</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <v>7800</v>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Баскунчак</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Уралкалий</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Уралкалий</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>perevalka-tsk.ru</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Баскунчак</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>навалом / биг-бэг</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>8700</v>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>самовывоз</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>https://perevalka-tsk.ru/product/pg-materialy/tekhnicheskaya-sol/tekhnicheskaya-sol-araltuz/</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>opt6.ru</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>МКР, помол 2 тип Б</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>9990</v>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>«от»</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>https://opt6.ru/products/tekhnicheskaya_sol_mkr/</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>sknerud.ru</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Тыреть / Илецксоль</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>МКР 1 т</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>«от», доставка отдельно</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>https://sknerud.ru/reagent/sol-texnicheskaya/</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>vektor-e.ru</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Илецкая</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>МКР / россыпь</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>с НДС, без доставки</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>https://vektor-e.ru/sol/</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Руссоль-центр</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Руссоль</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>мешки/МКР, от 10 т</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="12" t="n">
         <v>11300</v>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>опт, по данным выдачи поиска (сайт 403)</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>https://www.xn----jtbqkblfcapd5b2e.xn--p1ai/catalog/k-6070503-sol_tekhnicheskaya</t>
         </is>
@@ -4875,5 +4918,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>